--- a/artfynd/A 15171-2022 artfynd.xlsx
+++ b/artfynd/A 15171-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 15171-2022 artfynd.xlsx
+++ b/artfynd/A 15171-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>56014357</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597549.0113341608</v>
+        <v>597549</v>
       </c>
       <c r="R2" t="n">
-        <v>7339423.987750992</v>
+        <v>7339424</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>2015-08-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-08-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>56014356</v>
+        <v>56014359</v>
       </c>
       <c r="B3" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597549.0113341608</v>
+        <v>597549</v>
       </c>
       <c r="R3" t="n">
-        <v>7339423.987750992</v>
+        <v>7339424</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -860,19 +840,9 @@
           <t>2015-08-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2015-08-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,118 +866,6 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>56014359</v>
-      </c>
-      <c r="B4" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Biksa priv, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>597549.0113341608</v>
-      </c>
-      <c r="R4" t="n">
-        <v>7339423.987750992</v>
-      </c>
-      <c r="S4" t="n">
-        <v>50</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2015-08-12</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2015-08-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Sture Westerberg</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Sture Westerberg, Mary Agrér, Robert Sandberg</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15171-2022 artfynd.xlsx
+++ b/artfynd/A 15171-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -867,6 +867,103 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135140957</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106309</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Björnberget, Björnberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>597358</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7339583</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 15171-2022 artfynd.xlsx
+++ b/artfynd/A 15171-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56014357</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56014359</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,8 +978,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135140957</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 15171-2022 artfynd.xlsx
+++ b/artfynd/A 15171-2022 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>135140957</v>
       </c>
       <c r="B4" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 15171-2022 artfynd.xlsx
+++ b/artfynd/A 15171-2022 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>135140957</v>
       </c>
       <c r="B4" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
